--- a/Evaluation/Reviewer Material/Evaluation Rubric.xlsx
+++ b/Evaluation/Reviewer Material/Evaluation Rubric.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bassant\Desktop\Papers\Stanford\Comment Files\Evaluation - Anonymized\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8399FCFD-0AE5-4AAE-AEE4-EED496C80C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA449413-E09B-4A0A-90CB-09A63F4CB891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{3177EB1A-883B-422D-8C8E-649FF2E20E76}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="17">
   <si>
     <t>Response 1</t>
   </si>
@@ -84,25 +84,13 @@
     <t>Question 3</t>
   </si>
   <si>
-    <t>Question 4</t>
-  </si>
-  <si>
-    <t>Question 5</t>
-  </si>
-  <si>
-    <t>Question 6</t>
-  </si>
-  <si>
-    <t>Question 7</t>
-  </si>
-  <si>
-    <t>Instructions: there are two sheets, one for the case questions and one for the theoretical questions. For each of the 5 criteria columns, fill in a number between 0 and 1, inclusive. If you would like to add comments to a particular number, you are welcome to do so: it will help me explain your results!</t>
-  </si>
-  <si>
     <t>Question</t>
   </si>
   <si>
     <t>Response</t>
+  </si>
+  <si>
+    <t>Instructions: there are two sheets, one for the case questions and one for the theoretical questions. For each of the 5 criteria columns, fill in a number between 0 and 5, inclusive. If you would like to add comments to a particular number, you are welcome to do so: it will help me explain your results!</t>
   </si>
 </sst>
 </file>
@@ -245,9 +233,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -256,6 +241,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -594,7 +582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C37AFA3-BE47-456F-A6BB-B5CB38037B9D}">
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.54296875" style="1" customWidth="1"/>
@@ -608,22 +596,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="8"/>
+      <c r="A1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="7"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>2</v>
@@ -642,7 +630,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -655,7 +643,7 @@
       <c r="G3" s="2"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="5"/>
+      <c r="A4" s="8"/>
       <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
@@ -666,7 +654,7 @@
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="5"/>
+      <c r="A5" s="8"/>
       <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
@@ -677,7 +665,7 @@
       <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="5"/>
+      <c r="A6" s="8"/>
       <c r="B6" s="3" t="s">
         <v>9</v>
       </c>
@@ -688,7 +676,7 @@
       <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="5"/>
+      <c r="A7" s="8"/>
       <c r="B7" s="3" t="s">
         <v>10</v>
       </c>
@@ -699,7 +687,7 @@
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="5"/>
+      <c r="A8" s="8"/>
       <c r="B8" s="3" t="s">
         <v>11</v>
       </c>
@@ -778,7 +766,7 @@
       <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -791,7 +779,7 @@
       <c r="G15" s="2"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="5"/>
+      <c r="A16" s="8"/>
       <c r="B16" s="3" t="s">
         <v>7</v>
       </c>
@@ -802,7 +790,7 @@
       <c r="G16" s="2"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="5"/>
+      <c r="A17" s="8"/>
       <c r="B17" s="3" t="s">
         <v>8</v>
       </c>
@@ -813,7 +801,7 @@
       <c r="G17" s="2"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" s="5"/>
+      <c r="A18" s="8"/>
       <c r="B18" s="3" t="s">
         <v>9</v>
       </c>
@@ -824,7 +812,7 @@
       <c r="G18" s="2"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" s="5"/>
+      <c r="A19" s="8"/>
       <c r="B19" s="3" t="s">
         <v>10</v>
       </c>
@@ -835,7 +823,7 @@
       <c r="G19" s="2"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" s="5"/>
+      <c r="A20" s="8"/>
       <c r="B20" s="3" t="s">
         <v>11</v>
       </c>
@@ -845,288 +833,12 @@
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A22" s="5"/>
-      <c r="B22" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A23" s="5"/>
-      <c r="B23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" s="5"/>
-      <c r="B24" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A25" s="5"/>
-      <c r="B25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" s="5"/>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A27" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A28" s="5"/>
-      <c r="B28" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29" s="5"/>
-      <c r="B29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30" s="5"/>
-      <c r="B30" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A31" s="5"/>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A32" s="5"/>
-      <c r="B32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A33" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A34" s="5"/>
-      <c r="B34" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A35" s="5"/>
-      <c r="B35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A36" s="5"/>
-      <c r="B36" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A37" s="5"/>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A38" s="5"/>
-      <c r="B38" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A39" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A40" s="5"/>
-      <c r="B40" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A41" s="5"/>
-      <c r="B41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A42" s="5"/>
-      <c r="B42" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A43" s="5"/>
-      <c r="B43" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A44" s="5"/>
-      <c r="B44" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-    </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A39:A44"/>
+  <mergeCells count="4">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A3:A8"/>
     <mergeCell ref="A9:A14"/>
     <mergeCell ref="A15:A20"/>
-    <mergeCell ref="A21:A26"/>
-    <mergeCell ref="A27:A32"/>
-    <mergeCell ref="A33:A38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1134,7 +846,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11948623-6361-462A-B223-BCBD4A1A5DEB}">
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.54296875" style="1" customWidth="1"/>
@@ -1148,22 +860,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="8"/>
+      <c r="A1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="7"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>2</v>
@@ -1182,7 +894,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -1195,7 +907,7 @@
       <c r="G3" s="2"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="5"/>
+      <c r="A4" s="8"/>
       <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
@@ -1206,7 +918,7 @@
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="5"/>
+      <c r="A5" s="8"/>
       <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
@@ -1217,7 +929,7 @@
       <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="5"/>
+      <c r="A6" s="8"/>
       <c r="B6" s="3" t="s">
         <v>9</v>
       </c>
@@ -1228,7 +940,7 @@
       <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="5"/>
+      <c r="A7" s="8"/>
       <c r="B7" s="3" t="s">
         <v>10</v>
       </c>
@@ -1239,7 +951,7 @@
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="5"/>
+      <c r="A8" s="8"/>
       <c r="B8" s="3" t="s">
         <v>11</v>
       </c>
@@ -1318,7 +1030,7 @@
       <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -1331,7 +1043,7 @@
       <c r="G15" s="2"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="5"/>
+      <c r="A16" s="8"/>
       <c r="B16" s="3" t="s">
         <v>7</v>
       </c>
@@ -1342,7 +1054,7 @@
       <c r="G16" s="2"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="5"/>
+      <c r="A17" s="8"/>
       <c r="B17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1353,7 +1065,7 @@
       <c r="G17" s="2"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" s="5"/>
+      <c r="A18" s="8"/>
       <c r="B18" s="3" t="s">
         <v>9</v>
       </c>
@@ -1364,7 +1076,7 @@
       <c r="G18" s="2"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" s="5"/>
+      <c r="A19" s="8"/>
       <c r="B19" s="3" t="s">
         <v>10</v>
       </c>
@@ -1375,7 +1087,7 @@
       <c r="G19" s="2"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" s="5"/>
+      <c r="A20" s="8"/>
       <c r="B20" s="3" t="s">
         <v>11</v>
       </c>
@@ -1385,288 +1097,12 @@
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A22" s="5"/>
-      <c r="B22" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A23" s="5"/>
-      <c r="B23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" s="5"/>
-      <c r="B24" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A25" s="5"/>
-      <c r="B25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" s="5"/>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A27" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A28" s="5"/>
-      <c r="B28" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29" s="5"/>
-      <c r="B29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30" s="5"/>
-      <c r="B30" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A31" s="5"/>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A32" s="5"/>
-      <c r="B32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A33" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A34" s="5"/>
-      <c r="B34" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A35" s="5"/>
-      <c r="B35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A36" s="5"/>
-      <c r="B36" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A37" s="5"/>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A38" s="5"/>
-      <c r="B38" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A39" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A40" s="5"/>
-      <c r="B40" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A41" s="5"/>
-      <c r="B41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A42" s="5"/>
-      <c r="B42" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A43" s="5"/>
-      <c r="B43" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A44" s="5"/>
-      <c r="B44" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-    </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A33:A38"/>
-    <mergeCell ref="A39:A44"/>
+  <mergeCells count="4">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A3:A8"/>
     <mergeCell ref="A9:A14"/>
     <mergeCell ref="A15:A20"/>
-    <mergeCell ref="A21:A26"/>
-    <mergeCell ref="A27:A32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
